--- a/data/processed/positivacao/2025-04_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2025-04_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -27363,7 +27363,7 @@
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1040" t="inlineStr"/>
@@ -38429,7 +38429,7 @@
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1466" t="inlineStr"/>
@@ -66463,7 +66463,7 @@
     <row r="2545">
       <c r="A2545" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2545" t="inlineStr"/>
@@ -68108,12 +68108,12 @@
       <c r="A2609" t="inlineStr"/>
       <c r="B2609" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 4 cliente(s), não positivou 86 cliente(s) - Total vendido: R$ 1.913,78
+          <t>Vendedor 1 - VENDEDOR 01: positivou 4 cliente(s), não positivou 86 cliente(s) - Total vendido: R$ 1.913,78
 Vendedor 18 - LOJA: positivou 282 cliente(s), não positivou 658 cliente(s) - Total vendido: R$ 148.080,13
-Vendedor 3 - FERNANDA: positivou 113 cliente(s), não positivou 312 cliente(s) - Total vendido: R$ 132.964,91
-Vendedor 4 - DANIELA: positivou 136 cliente(s), não positivou 498 cliente(s) - Total vendido: R$ 70.896,34
+Vendedor 3 - VENDEDOR 03: positivou 113 cliente(s), não positivou 312 cliente(s) - Total vendido: R$ 132.964,91
+Vendedor 4 - VENDEDOR 04: positivou 136 cliente(s), não positivou 498 cliente(s) - Total vendido: R$ 70.896,34
 Vendedor 5 - SITE: positivou 4 cliente(s), não positivou 439 cliente(s) - Total vendido: R$ 1.291,59
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 62 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 62 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2609" t="inlineStr"/>
